--- a/data/H131_20260621_18.xlsx
+++ b/data/H131_20260621_18.xlsx
@@ -264,7 +264,7 @@
         <v>13.0</v>
       </c>
       <c r="S2" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="T2" t="n">
         <v>6.0</v>
@@ -276,7 +276,7 @@
         <v>0.0</v>
       </c>
       <c r="W2" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="3">
@@ -379,7 +379,7 @@
         <v>1074.0</v>
       </c>
       <c r="J4" t="n">
-        <v>800.0</v>
+        <v>801.0</v>
       </c>
       <c r="K4" t="n">
         <v>1.0</v>
@@ -391,10 +391,10 @@
         <v>0.0</v>
       </c>
       <c r="N4" t="n">
-        <v>800.0</v>
+        <v>801.0</v>
       </c>
       <c r="O4" t="n">
-        <v>443.0</v>
+        <v>444.0</v>
       </c>
       <c r="P4" t="n">
         <v>357.0</v>
@@ -403,10 +403,10 @@
         <v>0.0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T4" t="n">
         <v>0.0</v>
@@ -418,7 +418,7 @@
         <v>0.0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="5">
@@ -450,7 +450,7 @@
         <v>667.0</v>
       </c>
       <c r="J5" t="n">
-        <v>627.0</v>
+        <v>629.0</v>
       </c>
       <c r="K5" t="n">
         <v>1.0</v>
@@ -462,16 +462,16 @@
         <v>0.0</v>
       </c>
       <c r="N5" t="n">
-        <v>627.0</v>
+        <v>629.0</v>
       </c>
       <c r="O5" t="n">
         <v>333.0</v>
       </c>
       <c r="P5" t="n">
-        <v>293.0</v>
+        <v>294.0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R5" t="n">
         <v>24.0</v>
@@ -521,7 +521,7 @@
         <v>929.0</v>
       </c>
       <c r="J6" t="n">
-        <v>841.0</v>
+        <v>849.0</v>
       </c>
       <c r="K6" t="n">
         <v>1.0</v>
@@ -533,13 +533,13 @@
         <v>0.0</v>
       </c>
       <c r="N6" t="n">
-        <v>841.0</v>
+        <v>849.0</v>
       </c>
       <c r="O6" t="n">
-        <v>450.0</v>
+        <v>456.0</v>
       </c>
       <c r="P6" t="n">
-        <v>391.0</v>
+        <v>393.0</v>
       </c>
       <c r="Q6" t="n">
         <v>0.0</v>
@@ -548,7 +548,7 @@
         <v>37.0</v>
       </c>
       <c r="S6" t="n">
-        <v>14.0</v>
+        <v>18.0</v>
       </c>
       <c r="T6" t="n">
         <v>3.0</v>
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="W6" t="n">
-        <v>54.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="7">
@@ -734,7 +734,7 @@
         <v>730.0</v>
       </c>
       <c r="J9" t="n">
-        <v>651.0</v>
+        <v>658.0</v>
       </c>
       <c r="K9" t="n">
         <v>1.0</v>
@@ -746,13 +746,13 @@
         <v>0.0</v>
       </c>
       <c r="N9" t="n">
-        <v>651.0</v>
+        <v>658.0</v>
       </c>
       <c r="O9" t="n">
-        <v>363.0</v>
+        <v>368.0</v>
       </c>
       <c r="P9" t="n">
-        <v>288.0</v>
+        <v>290.0</v>
       </c>
       <c r="Q9" t="n">
         <v>0.0</v>
@@ -980,13 +980,13 @@
         <v>0.0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="V12" t="n">
         <v>0.0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="13">
@@ -1231,7 +1231,7 @@
         <v>692.0</v>
       </c>
       <c r="J16" t="n">
-        <v>580.0</v>
+        <v>581.0</v>
       </c>
       <c r="K16" t="n">
         <v>1.0</v>
@@ -1243,13 +1243,13 @@
         <v>0.0</v>
       </c>
       <c r="N16" t="n">
-        <v>580.0</v>
+        <v>581.0</v>
       </c>
       <c r="O16" t="n">
         <v>285.0</v>
       </c>
       <c r="P16" t="n">
-        <v>295.0</v>
+        <v>296.0</v>
       </c>
       <c r="Q16" t="n">
         <v>0.0</v>
@@ -1728,7 +1728,7 @@
         <v>762.0</v>
       </c>
       <c r="J23" t="n">
-        <v>698.0</v>
+        <v>713.0</v>
       </c>
       <c r="K23" t="n">
         <v>1.0</v>
@@ -1740,13 +1740,13 @@
         <v>0.0</v>
       </c>
       <c r="N23" t="n">
-        <v>698.0</v>
+        <v>713.0</v>
       </c>
       <c r="O23" t="n">
-        <v>379.0</v>
+        <v>390.0</v>
       </c>
       <c r="P23" t="n">
-        <v>319.0</v>
+        <v>323.0</v>
       </c>
       <c r="Q23" t="n">
         <v>0.0</v>
@@ -1799,7 +1799,7 @@
         <v>1296.0</v>
       </c>
       <c r="J24" t="n">
-        <v>1163.0</v>
+        <v>1170.0</v>
       </c>
       <c r="K24" t="n">
         <v>1.0</v>
@@ -1811,13 +1811,13 @@
         <v>0.0</v>
       </c>
       <c r="N24" t="n">
-        <v>1163.0</v>
+        <v>1170.0</v>
       </c>
       <c r="O24" t="n">
-        <v>709.0</v>
+        <v>714.0</v>
       </c>
       <c r="P24" t="n">
-        <v>437.0</v>
+        <v>439.0</v>
       </c>
       <c r="Q24" t="n">
         <v>17.0</v>
@@ -1941,7 +1941,7 @@
         <v>1399.0</v>
       </c>
       <c r="J26" t="n">
-        <v>1255.0</v>
+        <v>1288.0</v>
       </c>
       <c r="K26" t="n">
         <v>1.0</v>
@@ -1953,7 +1953,7 @@
         <v>0.0</v>
       </c>
       <c r="N26" t="n">
-        <v>1255.0</v>
+        <v>1288.0</v>
       </c>
       <c r="O26" t="n">
         <v>673.0</v>
@@ -1962,7 +1962,7 @@
         <v>555.0</v>
       </c>
       <c r="Q26" t="n">
-        <v>27.0</v>
+        <v>60.0</v>
       </c>
       <c r="R26" t="n">
         <v>47.0</v>
@@ -2083,7 +2083,7 @@
         <v>1349.0</v>
       </c>
       <c r="J28" t="n">
-        <v>1141.0</v>
+        <v>1152.0</v>
       </c>
       <c r="K28" t="n">
         <v>1.0</v>
@@ -2095,13 +2095,13 @@
         <v>0.0</v>
       </c>
       <c r="N28" t="n">
-        <v>1141.0</v>
+        <v>1152.0</v>
       </c>
       <c r="O28" t="n">
-        <v>642.0</v>
+        <v>651.0</v>
       </c>
       <c r="P28" t="n">
-        <v>497.0</v>
+        <v>499.0</v>
       </c>
       <c r="Q28" t="n">
         <v>2.0</v>
@@ -2154,7 +2154,7 @@
         <v>1280.0</v>
       </c>
       <c r="J29" t="n">
-        <v>833.0</v>
+        <v>850.0</v>
       </c>
       <c r="K29" t="n">
         <v>1.0</v>
@@ -2166,13 +2166,13 @@
         <v>0.0</v>
       </c>
       <c r="N29" t="n">
-        <v>833.0</v>
+        <v>850.0</v>
       </c>
       <c r="O29" t="n">
-        <v>295.0</v>
+        <v>307.0</v>
       </c>
       <c r="P29" t="n">
-        <v>406.0</v>
+        <v>411.0</v>
       </c>
       <c r="Q29" t="n">
         <v>132.0</v>
@@ -2296,7 +2296,7 @@
         <v>1214.0</v>
       </c>
       <c r="J31" t="n">
-        <v>1077.0</v>
+        <v>1078.0</v>
       </c>
       <c r="K31" t="n">
         <v>1.0</v>
@@ -2308,10 +2308,10 @@
         <v>0.0</v>
       </c>
       <c r="N31" t="n">
-        <v>1077.0</v>
+        <v>1078.0</v>
       </c>
       <c r="O31" t="n">
-        <v>592.0</v>
+        <v>593.0</v>
       </c>
       <c r="P31" t="n">
         <v>471.0</v>
@@ -2367,7 +2367,7 @@
         <v>1143.0</v>
       </c>
       <c r="J32" t="n">
-        <v>905.0</v>
+        <v>917.0</v>
       </c>
       <c r="K32" t="n">
         <v>1.0</v>
@@ -2379,16 +2379,16 @@
         <v>0.0</v>
       </c>
       <c r="N32" t="n">
-        <v>905.0</v>
+        <v>917.0</v>
       </c>
       <c r="O32" t="n">
-        <v>432.0</v>
+        <v>437.0</v>
       </c>
       <c r="P32" t="n">
-        <v>443.0</v>
+        <v>449.0</v>
       </c>
       <c r="Q32" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="R32" t="n">
         <v>14.0</v>
@@ -2400,13 +2400,13 @@
         <v>5.0</v>
       </c>
       <c r="U32" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="V32" t="n">
         <v>0.0</v>
       </c>
       <c r="W32" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="33">
@@ -2651,7 +2651,7 @@
         <v>1103.0</v>
       </c>
       <c r="J36" t="n">
-        <v>884.0</v>
+        <v>901.0</v>
       </c>
       <c r="K36" t="n">
         <v>1.0</v>
@@ -2663,16 +2663,16 @@
         <v>0.0</v>
       </c>
       <c r="N36" t="n">
-        <v>884.0</v>
+        <v>901.0</v>
       </c>
       <c r="O36" t="n">
-        <v>436.0</v>
+        <v>450.0</v>
       </c>
       <c r="P36" t="n">
-        <v>430.0</v>
+        <v>432.0</v>
       </c>
       <c r="Q36" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="R36" t="n">
         <v>45.0</v>
@@ -3148,7 +3148,7 @@
         <v>1022.0</v>
       </c>
       <c r="J43" t="n">
-        <v>944.0</v>
+        <v>952.0</v>
       </c>
       <c r="K43" t="n">
         <v>1.0</v>
@@ -3160,13 +3160,13 @@
         <v>0.0</v>
       </c>
       <c r="N43" t="n">
-        <v>944.0</v>
+        <v>952.0</v>
       </c>
       <c r="O43" t="n">
-        <v>491.0</v>
+        <v>496.0</v>
       </c>
       <c r="P43" t="n">
-        <v>441.0</v>
+        <v>444.0</v>
       </c>
       <c r="Q43" t="n">
         <v>12.0</v>
@@ -3175,7 +3175,7 @@
         <v>30.0</v>
       </c>
       <c r="S43" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T43" t="n">
         <v>2.0</v>
@@ -3187,7 +3187,7 @@
         <v>0.0</v>
       </c>
       <c r="W43" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="44">
@@ -3574,7 +3574,7 @@
         <v>1437.0</v>
       </c>
       <c r="J49" t="n">
-        <v>1343.0</v>
+        <v>1345.0</v>
       </c>
       <c r="K49" t="n">
         <v>1.0</v>
@@ -3586,10 +3586,10 @@
         <v>0.0</v>
       </c>
       <c r="N49" t="n">
-        <v>1343.0</v>
+        <v>1345.0</v>
       </c>
       <c r="O49" t="n">
-        <v>771.0</v>
+        <v>773.0</v>
       </c>
       <c r="P49" t="n">
         <v>533.0</v>
@@ -4953,7 +4953,7 @@
         <v>24.0</v>
       </c>
       <c r="T68" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U68" t="n">
         <v>0.0</v>
@@ -4962,7 +4962,7 @@
         <v>0.0</v>
       </c>
       <c r="W68" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="69">
@@ -4994,7 +4994,7 @@
         <v>1125.0</v>
       </c>
       <c r="J69" t="n">
-        <v>1096.0</v>
+        <v>1107.0</v>
       </c>
       <c r="K69" t="n">
         <v>1.0</v>
@@ -5006,22 +5006,22 @@
         <v>1.0</v>
       </c>
       <c r="N69" t="n">
-        <v>1095.0</v>
+        <v>1106.0</v>
       </c>
       <c r="O69" t="n">
-        <v>604.0</v>
+        <v>607.0</v>
       </c>
       <c r="P69" t="n">
-        <v>492.0</v>
+        <v>493.0</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="R69" t="n">
         <v>0.0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T69" t="n">
         <v>0.0</v>
@@ -5033,7 +5033,7 @@
         <v>0.0</v>
       </c>
       <c r="W69" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="70">
@@ -5657,22 +5657,22 @@
         <v>0.0</v>
       </c>
       <c r="R78" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="S78" t="n">
-        <v>1.0</v>
+        <v>42.0</v>
       </c>
       <c r="T78" t="n">
         <v>0.0</v>
       </c>
       <c r="U78" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V78" t="n">
         <v>0.0</v>
       </c>
       <c r="W78" t="n">
-        <v>51.0</v>
+        <v>94.0</v>
       </c>
     </row>
     <row r="79">
@@ -5704,7 +5704,7 @@
         <v>787.0</v>
       </c>
       <c r="J79" t="n">
-        <v>707.0</v>
+        <v>709.0</v>
       </c>
       <c r="K79" t="n">
         <v>1.0</v>
@@ -5716,10 +5716,10 @@
         <v>0.0</v>
       </c>
       <c r="N79" t="n">
-        <v>707.0</v>
+        <v>709.0</v>
       </c>
       <c r="O79" t="n">
-        <v>443.0</v>
+        <v>445.0</v>
       </c>
       <c r="P79" t="n">
         <v>264.0</v>
@@ -5731,10 +5731,10 @@
         <v>24.0</v>
       </c>
       <c r="S79" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="T79" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="U79" t="n">
         <v>0.0</v>
@@ -5743,7 +5743,7 @@
         <v>0.0</v>
       </c>
       <c r="W79" t="n">
-        <v>54.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="80">
@@ -5775,7 +5775,7 @@
         <v>1333.0</v>
       </c>
       <c r="J80" t="n">
-        <v>1185.0</v>
+        <v>1203.0</v>
       </c>
       <c r="K80" t="n">
         <v>1.0</v>
@@ -5787,13 +5787,13 @@
         <v>0.0</v>
       </c>
       <c r="N80" t="n">
-        <v>1185.0</v>
+        <v>1203.0</v>
       </c>
       <c r="O80" t="n">
-        <v>643.0</v>
+        <v>650.0</v>
       </c>
       <c r="P80" t="n">
-        <v>535.0</v>
+        <v>546.0</v>
       </c>
       <c r="Q80" t="n">
         <v>7.0</v>
@@ -5917,7 +5917,7 @@
         <v>1157.0</v>
       </c>
       <c r="J82" t="n">
-        <v>960.0</v>
+        <v>963.0</v>
       </c>
       <c r="K82" t="n">
         <v>1.0</v>
@@ -5929,10 +5929,10 @@
         <v>0.0</v>
       </c>
       <c r="N82" t="n">
-        <v>960.0</v>
+        <v>963.0</v>
       </c>
       <c r="O82" t="n">
-        <v>486.0</v>
+        <v>489.0</v>
       </c>
       <c r="P82" t="n">
         <v>474.0</v>
@@ -5941,7 +5941,7 @@
         <v>0.0</v>
       </c>
       <c r="R82" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="S82" t="n">
         <v>28.0</v>
@@ -5956,7 +5956,7 @@
         <v>0.0</v>
       </c>
       <c r="W82" t="n">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="83">
@@ -5988,7 +5988,7 @@
         <v>1127.0</v>
       </c>
       <c r="J83" t="n">
-        <v>946.0</v>
+        <v>970.0</v>
       </c>
       <c r="K83" t="n">
         <v>1.0</v>
@@ -6000,13 +6000,13 @@
         <v>0.0</v>
       </c>
       <c r="N83" t="n">
-        <v>946.0</v>
+        <v>970.0</v>
       </c>
       <c r="O83" t="n">
-        <v>506.0</v>
+        <v>527.0</v>
       </c>
       <c r="P83" t="n">
-        <v>440.0</v>
+        <v>443.0</v>
       </c>
       <c r="Q83" t="n">
         <v>0.0</v>
@@ -6015,7 +6015,7 @@
         <v>35.0</v>
       </c>
       <c r="S83" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="T83" t="n">
         <v>1.0</v>
@@ -6027,7 +6027,7 @@
         <v>0.0</v>
       </c>
       <c r="W83" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="84">
@@ -6201,7 +6201,7 @@
         <v>1249.0</v>
       </c>
       <c r="J86" t="n">
-        <v>1204.0</v>
+        <v>1208.0</v>
       </c>
       <c r="K86" t="n">
         <v>1.0</v>
@@ -6213,16 +6213,16 @@
         <v>0.0</v>
       </c>
       <c r="N86" t="n">
-        <v>1204.0</v>
+        <v>1208.0</v>
       </c>
       <c r="O86" t="n">
-        <v>675.0</v>
+        <v>678.0</v>
       </c>
       <c r="P86" t="n">
         <v>529.0</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R86" t="n">
         <v>9.0</v>
@@ -6627,7 +6627,7 @@
         <v>1315.0</v>
       </c>
       <c r="J92" t="n">
-        <v>1017.0</v>
+        <v>1033.0</v>
       </c>
       <c r="K92" t="n">
         <v>1.0</v>
@@ -6639,34 +6639,34 @@
         <v>0.0</v>
       </c>
       <c r="N92" t="n">
-        <v>1017.0</v>
+        <v>1033.0</v>
       </c>
       <c r="O92" t="n">
-        <v>525.0</v>
+        <v>538.0</v>
       </c>
       <c r="P92" t="n">
-        <v>383.0</v>
+        <v>385.0</v>
       </c>
       <c r="Q92" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="R92" t="n">
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
       <c r="S92" t="n">
-        <v>117.0</v>
+        <v>118.0</v>
       </c>
       <c r="T92" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U92" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="V92" t="n">
         <v>2.0</v>
       </c>
       <c r="W92" t="n">
-        <v>196.0</v>
+        <v>201.0</v>
       </c>
     </row>
     <row r="93">
@@ -6769,7 +6769,7 @@
         <v>833.0</v>
       </c>
       <c r="J94" t="n">
-        <v>725.0</v>
+        <v>738.0</v>
       </c>
       <c r="K94" t="n">
         <v>1.0</v>
@@ -6781,13 +6781,13 @@
         <v>0.0</v>
       </c>
       <c r="N94" t="n">
-        <v>725.0</v>
+        <v>738.0</v>
       </c>
       <c r="O94" t="n">
+        <v>373.0</v>
+      </c>
+      <c r="P94" t="n">
         <v>363.0</v>
-      </c>
-      <c r="P94" t="n">
-        <v>360.0</v>
       </c>
       <c r="Q94" t="n">
         <v>2.0</v>
@@ -7053,7 +7053,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" t="n">
-        <v>1352.0</v>
+        <v>1354.0</v>
       </c>
       <c r="K98" t="n">
         <v>1.0</v>
@@ -7065,13 +7065,13 @@
         <v>0.0</v>
       </c>
       <c r="N98" t="n">
-        <v>1352.0</v>
+        <v>1354.0</v>
       </c>
       <c r="O98" t="n">
-        <v>723.0</v>
+        <v>724.0</v>
       </c>
       <c r="P98" t="n">
-        <v>619.0</v>
+        <v>620.0</v>
       </c>
       <c r="Q98" t="n">
         <v>10.0</v>
@@ -7692,7 +7692,7 @@
         <v>1053.0</v>
       </c>
       <c r="J107" t="n">
-        <v>845.0</v>
+        <v>847.0</v>
       </c>
       <c r="K107" t="n">
         <v>1.0</v>
@@ -7704,13 +7704,13 @@
         <v>0.0</v>
       </c>
       <c r="N107" t="n">
-        <v>845.0</v>
+        <v>847.0</v>
       </c>
       <c r="O107" t="n">
-        <v>446.0</v>
+        <v>447.0</v>
       </c>
       <c r="P107" t="n">
-        <v>399.0</v>
+        <v>400.0</v>
       </c>
       <c r="Q107" t="n">
         <v>0.0</v>
@@ -7905,7 +7905,7 @@
         <v>754.0</v>
       </c>
       <c r="J110" t="n">
-        <v>652.0</v>
+        <v>655.0</v>
       </c>
       <c r="K110" t="n">
         <v>1.0</v>
@@ -7917,19 +7917,19 @@
         <v>0.0</v>
       </c>
       <c r="N110" t="n">
-        <v>652.0</v>
+        <v>655.0</v>
       </c>
       <c r="O110" t="n">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="P110" t="n">
-        <v>305.0</v>
+        <v>307.0</v>
       </c>
       <c r="Q110" t="n">
         <v>19.0</v>
       </c>
       <c r="R110" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="S110" t="n">
         <v>49.0</v>
@@ -7944,7 +7944,7 @@
         <v>0.0</v>
       </c>
       <c r="W110" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="111">
@@ -8118,7 +8118,7 @@
         <v>921.0</v>
       </c>
       <c r="J113" t="n">
-        <v>891.0</v>
+        <v>892.0</v>
       </c>
       <c r="K113" t="n">
         <v>1.0</v>
@@ -8130,10 +8130,10 @@
         <v>0.0</v>
       </c>
       <c r="N113" t="n">
-        <v>891.0</v>
+        <v>892.0</v>
       </c>
       <c r="O113" t="n">
-        <v>453.0</v>
+        <v>454.0</v>
       </c>
       <c r="P113" t="n">
         <v>438.0</v>
@@ -8145,7 +8145,7 @@
         <v>1.0</v>
       </c>
       <c r="S113" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T113" t="n">
         <v>0.0</v>
@@ -8157,7 +8157,7 @@
         <v>0.0</v>
       </c>
       <c r="W113" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="114">
@@ -8189,7 +8189,7 @@
         <v>924.0</v>
       </c>
       <c r="J114" t="n">
-        <v>824.0</v>
+        <v>831.0</v>
       </c>
       <c r="K114" t="n">
         <v>1.0</v>
@@ -8201,13 +8201,13 @@
         <v>0.0</v>
       </c>
       <c r="N114" t="n">
-        <v>824.0</v>
+        <v>831.0</v>
       </c>
       <c r="O114" t="n">
-        <v>496.0</v>
+        <v>500.0</v>
       </c>
       <c r="P114" t="n">
-        <v>327.0</v>
+        <v>330.0</v>
       </c>
       <c r="Q114" t="n">
         <v>1.0</v>
@@ -8216,7 +8216,7 @@
         <v>26.0</v>
       </c>
       <c r="S114" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="T114" t="n">
         <v>0.0</v>
@@ -8228,7 +8228,7 @@
         <v>0.0</v>
       </c>
       <c r="W114" t="n">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="115">
@@ -8260,7 +8260,7 @@
         <v>1337.0</v>
       </c>
       <c r="J115" t="n">
-        <v>1022.0</v>
+        <v>1024.0</v>
       </c>
       <c r="K115" t="n">
         <v>1.0</v>
@@ -8272,10 +8272,10 @@
         <v>0.0</v>
       </c>
       <c r="N115" t="n">
-        <v>1022.0</v>
+        <v>1024.0</v>
       </c>
       <c r="O115" t="n">
-        <v>454.0</v>
+        <v>456.0</v>
       </c>
       <c r="P115" t="n">
         <v>568.0</v>
@@ -8287,7 +8287,7 @@
         <v>41.0</v>
       </c>
       <c r="S115" t="n">
-        <v>13.0</v>
+        <v>34.0</v>
       </c>
       <c r="T115" t="n">
         <v>1.0</v>
@@ -8299,7 +8299,7 @@
         <v>0.0</v>
       </c>
       <c r="W115" t="n">
-        <v>136.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="116">
@@ -8402,7 +8402,7 @@
         <v>1078.0</v>
       </c>
       <c r="J117" t="n">
-        <v>774.0</v>
+        <v>795.0</v>
       </c>
       <c r="K117" t="n">
         <v>1.0</v>
@@ -8414,22 +8414,22 @@
         <v>1.0</v>
       </c>
       <c r="N117" t="n">
-        <v>773.0</v>
+        <v>794.0</v>
       </c>
       <c r="O117" t="n">
         <v>388.0</v>
       </c>
       <c r="P117" t="n">
-        <v>386.0</v>
+        <v>389.0</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="R117" t="n">
         <v>25.0</v>
       </c>
       <c r="S117" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="T117" t="n">
         <v>0.0</v>
@@ -8441,7 +8441,7 @@
         <v>0.0</v>
       </c>
       <c r="W117" t="n">
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="118">
@@ -8473,7 +8473,7 @@
         <v>1422.0</v>
       </c>
       <c r="J118" t="n">
-        <v>965.0</v>
+        <v>987.0</v>
       </c>
       <c r="K118" t="n">
         <v>1.0</v>
@@ -8485,13 +8485,13 @@
         <v>0.0</v>
       </c>
       <c r="N118" t="n">
-        <v>965.0</v>
+        <v>987.0</v>
       </c>
       <c r="O118" t="n">
-        <v>525.0</v>
+        <v>545.0</v>
       </c>
       <c r="P118" t="n">
-        <v>435.0</v>
+        <v>437.0</v>
       </c>
       <c r="Q118" t="n">
         <v>5.0</v>
@@ -8503,7 +8503,7 @@
         <v>19.0</v>
       </c>
       <c r="T118" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="U118" t="n">
         <v>16.0</v>
@@ -8512,7 +8512,7 @@
         <v>3.0</v>
       </c>
       <c r="W118" t="n">
-        <v>98.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="119">
@@ -8544,7 +8544,7 @@
         <v>1084.0</v>
       </c>
       <c r="J119" t="n">
-        <v>905.0</v>
+        <v>959.0</v>
       </c>
       <c r="K119" t="n">
         <v>1.0</v>
@@ -8556,34 +8556,34 @@
         <v>0.0</v>
       </c>
       <c r="N119" t="n">
-        <v>905.0</v>
+        <v>959.0</v>
       </c>
       <c r="O119" t="n">
-        <v>549.0</v>
+        <v>554.0</v>
       </c>
       <c r="P119" t="n">
-        <v>349.0</v>
+        <v>387.0</v>
       </c>
       <c r="Q119" t="n">
-        <v>7.0</v>
+        <v>18.0</v>
       </c>
       <c r="R119" t="n">
-        <v>62.0</v>
+        <v>69.0</v>
       </c>
       <c r="S119" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="T119" t="n">
         <v>0.0</v>
       </c>
       <c r="U119" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="V119" t="n">
         <v>0.0</v>
       </c>
       <c r="W119" t="n">
-        <v>87.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="120">
@@ -8615,7 +8615,7 @@
         <v>971.0</v>
       </c>
       <c r="J120" t="n">
-        <v>779.0</v>
+        <v>780.0</v>
       </c>
       <c r="K120" t="n">
         <v>1.0</v>
@@ -8627,13 +8627,13 @@
         <v>0.0</v>
       </c>
       <c r="N120" t="n">
-        <v>779.0</v>
+        <v>780.0</v>
       </c>
       <c r="O120" t="n">
         <v>440.0</v>
       </c>
       <c r="P120" t="n">
-        <v>334.0</v>
+        <v>335.0</v>
       </c>
       <c r="Q120" t="n">
         <v>5.0</v>
@@ -8757,7 +8757,7 @@
         <v>939.0</v>
       </c>
       <c r="J122" t="n">
-        <v>700.0</v>
+        <v>714.0</v>
       </c>
       <c r="K122" t="n">
         <v>1.0</v>
@@ -8769,13 +8769,13 @@
         <v>4.0</v>
       </c>
       <c r="N122" t="n">
-        <v>696.0</v>
+        <v>710.0</v>
       </c>
       <c r="O122" t="n">
-        <v>388.0</v>
+        <v>397.0</v>
       </c>
       <c r="P122" t="n">
-        <v>297.0</v>
+        <v>302.0</v>
       </c>
       <c r="Q122" t="n">
         <v>15.0</v>
@@ -9254,7 +9254,7 @@
         <v>1387.0</v>
       </c>
       <c r="J129" t="n">
-        <v>1035.0</v>
+        <v>1078.0</v>
       </c>
       <c r="K129" t="n">
         <v>1.0</v>
@@ -9266,34 +9266,34 @@
         <v>0.0</v>
       </c>
       <c r="N129" t="n">
-        <v>1035.0</v>
+        <v>1078.0</v>
       </c>
       <c r="O129" t="n">
-        <v>699.0</v>
+        <v>718.0</v>
       </c>
       <c r="P129" t="n">
-        <v>320.0</v>
+        <v>341.0</v>
       </c>
       <c r="Q129" t="n">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="R129" t="n">
-        <v>82.0</v>
+        <v>84.0</v>
       </c>
       <c r="S129" t="n">
-        <v>91.0</v>
+        <v>96.0</v>
       </c>
       <c r="T129" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="U129" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="V129" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="W129" t="n">
-        <v>230.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="130">
@@ -9396,7 +9396,7 @@
         <v>865.0</v>
       </c>
       <c r="J131" t="n">
-        <v>756.0</v>
+        <v>758.0</v>
       </c>
       <c r="K131" t="n">
         <v>1.0</v>
@@ -9408,13 +9408,13 @@
         <v>0.0</v>
       </c>
       <c r="N131" t="n">
-        <v>756.0</v>
+        <v>758.0</v>
       </c>
       <c r="O131" t="n">
         <v>393.0</v>
       </c>
       <c r="P131" t="n">
-        <v>343.0</v>
+        <v>345.0</v>
       </c>
       <c r="Q131" t="n">
         <v>20.0</v>
@@ -9467,7 +9467,7 @@
         <v>1427.0</v>
       </c>
       <c r="J132" t="n">
-        <v>1266.0</v>
+        <v>1343.0</v>
       </c>
       <c r="K132" t="n">
         <v>1.0</v>
@@ -9479,16 +9479,16 @@
         <v>0.0</v>
       </c>
       <c r="N132" t="n">
-        <v>1266.0</v>
+        <v>1343.0</v>
       </c>
       <c r="O132" t="n">
-        <v>708.0</v>
+        <v>759.0</v>
       </c>
       <c r="P132" t="n">
-        <v>535.0</v>
+        <v>560.0</v>
       </c>
       <c r="Q132" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="R132" t="n">
         <v>24.0</v>
@@ -9497,16 +9497,16 @@
         <v>3.0</v>
       </c>
       <c r="T132" t="n">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="U132" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="V132" t="n">
         <v>0.0</v>
       </c>
       <c r="W132" t="n">
-        <v>49.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="133">
@@ -9538,7 +9538,7 @@
         <v>1330.0</v>
       </c>
       <c r="J133" t="n">
-        <v>1198.0</v>
+        <v>1213.0</v>
       </c>
       <c r="K133" t="n">
         <v>1.0</v>
@@ -9550,22 +9550,22 @@
         <v>0.0</v>
       </c>
       <c r="N133" t="n">
-        <v>1198.0</v>
+        <v>1213.0</v>
       </c>
       <c r="O133" t="n">
-        <v>625.0</v>
+        <v>637.0</v>
       </c>
       <c r="P133" t="n">
-        <v>533.0</v>
+        <v>536.0</v>
       </c>
       <c r="Q133" t="n">
         <v>40.0</v>
       </c>
       <c r="R133" t="n">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
       <c r="S133" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="T133" t="n">
         <v>5.0</v>
@@ -9577,7 +9577,7 @@
         <v>0.0</v>
       </c>
       <c r="W133" t="n">
-        <v>105.0</v>
+        <v>108.0</v>
       </c>
     </row>
     <row r="134">
@@ -9822,7 +9822,7 @@
         <v>1211.0</v>
       </c>
       <c r="J137" t="n">
-        <v>972.0</v>
+        <v>994.0</v>
       </c>
       <c r="K137" t="n">
         <v>1.0</v>
@@ -9834,16 +9834,16 @@
         <v>0.0</v>
       </c>
       <c r="N137" t="n">
-        <v>972.0</v>
+        <v>994.0</v>
       </c>
       <c r="O137" t="n">
-        <v>521.0</v>
+        <v>538.0</v>
       </c>
       <c r="P137" t="n">
-        <v>424.0</v>
+        <v>425.0</v>
       </c>
       <c r="Q137" t="n">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
       <c r="R137" t="n">
         <v>48.0</v>
@@ -9855,13 +9855,13 @@
         <v>0.0</v>
       </c>
       <c r="U137" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="V137" t="n">
         <v>0.0</v>
       </c>
       <c r="W137" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="138">
@@ -9964,7 +9964,7 @@
         <v>1300.0</v>
       </c>
       <c r="J139" t="n">
-        <v>1038.0</v>
+        <v>1063.0</v>
       </c>
       <c r="K139" t="n">
         <v>1.0</v>
@@ -9976,19 +9976,19 @@
         <v>0.0</v>
       </c>
       <c r="N139" t="n">
-        <v>1038.0</v>
+        <v>1063.0</v>
       </c>
       <c r="O139" t="n">
-        <v>639.0</v>
+        <v>654.0</v>
       </c>
       <c r="P139" t="n">
-        <v>376.0</v>
+        <v>386.0</v>
       </c>
       <c r="Q139" t="n">
         <v>23.0</v>
       </c>
       <c r="R139" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="S139" t="n">
         <v>102.0</v>
@@ -10003,7 +10003,7 @@
         <v>0.0</v>
       </c>
       <c r="W139" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
     </row>
     <row r="140">
@@ -10035,7 +10035,7 @@
         <v>1236.0</v>
       </c>
       <c r="J140" t="n">
-        <v>911.0</v>
+        <v>923.0</v>
       </c>
       <c r="K140" t="n">
         <v>1.0</v>
@@ -10047,19 +10047,19 @@
         <v>0.0</v>
       </c>
       <c r="N140" t="n">
-        <v>911.0</v>
+        <v>923.0</v>
       </c>
       <c r="O140" t="n">
-        <v>482.0</v>
+        <v>488.0</v>
       </c>
       <c r="P140" t="n">
-        <v>422.0</v>
+        <v>428.0</v>
       </c>
       <c r="Q140" t="n">
         <v>7.0</v>
       </c>
       <c r="R140" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="S140" t="n">
         <v>78.0</v>
@@ -10074,7 +10074,7 @@
         <v>0.0</v>
       </c>
       <c r="W140" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="141">
@@ -10106,7 +10106,7 @@
         <v>1244.0</v>
       </c>
       <c r="J141" t="n">
-        <v>963.0</v>
+        <v>1039.0</v>
       </c>
       <c r="K141" t="n">
         <v>1.0</v>
@@ -10118,16 +10118,16 @@
         <v>1.0</v>
       </c>
       <c r="N141" t="n">
-        <v>962.0</v>
+        <v>1038.0</v>
       </c>
       <c r="O141" t="n">
-        <v>597.0</v>
+        <v>647.0</v>
       </c>
       <c r="P141" t="n">
-        <v>364.0</v>
+        <v>382.0</v>
       </c>
       <c r="Q141" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="R141" t="n">
         <v>24.0</v>
@@ -10136,16 +10136,16 @@
         <v>3.0</v>
       </c>
       <c r="T141" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U141" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="V141" t="n">
         <v>0.0</v>
       </c>
       <c r="W141" t="n">
-        <v>32.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="142">
@@ -10248,7 +10248,7 @@
         <v>1469.0</v>
       </c>
       <c r="J143" t="n">
-        <v>937.0</v>
+        <v>969.0</v>
       </c>
       <c r="K143" t="n">
         <v>1.0</v>
@@ -10260,13 +10260,13 @@
         <v>1.0</v>
       </c>
       <c r="N143" t="n">
-        <v>936.0</v>
+        <v>968.0</v>
       </c>
       <c r="O143" t="n">
-        <v>558.0</v>
+        <v>576.0</v>
       </c>
       <c r="P143" t="n">
-        <v>378.0</v>
+        <v>392.0</v>
       </c>
       <c r="Q143" t="n">
         <v>1.0</v>
@@ -10319,7 +10319,7 @@
         <v>1487.0</v>
       </c>
       <c r="J144" t="n">
-        <v>1123.0</v>
+        <v>1126.0</v>
       </c>
       <c r="K144" t="n">
         <v>1.0</v>
@@ -10331,13 +10331,13 @@
         <v>0.0</v>
       </c>
       <c r="N144" t="n">
-        <v>1123.0</v>
+        <v>1126.0</v>
       </c>
       <c r="O144" t="n">
         <v>635.0</v>
       </c>
       <c r="P144" t="n">
-        <v>488.0</v>
+        <v>491.0</v>
       </c>
       <c r="Q144" t="n">
         <v>0.0</v>
@@ -10390,7 +10390,7 @@
         <v>1012.0</v>
       </c>
       <c r="J145" t="n">
-        <v>908.0</v>
+        <v>913.0</v>
       </c>
       <c r="K145" t="n">
         <v>1.0</v>
@@ -10402,16 +10402,16 @@
         <v>0.0</v>
       </c>
       <c r="N145" t="n">
-        <v>908.0</v>
+        <v>913.0</v>
       </c>
       <c r="O145" t="n">
         <v>408.0</v>
       </c>
       <c r="P145" t="n">
-        <v>465.0</v>
+        <v>469.0</v>
       </c>
       <c r="Q145" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="R145" t="n">
         <v>18.0</v>
@@ -10423,13 +10423,13 @@
         <v>5.0</v>
       </c>
       <c r="U145" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="V145" t="n">
         <v>1.0</v>
       </c>
       <c r="W145" t="n">
-        <v>59.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="146">
@@ -10674,7 +10674,7 @@
         <v>1218.0</v>
       </c>
       <c r="J149" t="n">
-        <v>669.0</v>
+        <v>700.0</v>
       </c>
       <c r="K149" t="n">
         <v>1.0</v>
@@ -10686,13 +10686,13 @@
         <v>0.0</v>
       </c>
       <c r="N149" t="n">
-        <v>669.0</v>
+        <v>700.0</v>
       </c>
       <c r="O149" t="n">
-        <v>398.0</v>
+        <v>417.0</v>
       </c>
       <c r="P149" t="n">
-        <v>266.0</v>
+        <v>278.0</v>
       </c>
       <c r="Q149" t="n">
         <v>5.0</v>
@@ -11029,7 +11029,7 @@
         <v>999.0</v>
       </c>
       <c r="J154" t="n">
-        <v>718.0</v>
+        <v>740.0</v>
       </c>
       <c r="K154" t="n">
         <v>1.0</v>
@@ -11041,13 +11041,13 @@
         <v>0.0</v>
       </c>
       <c r="N154" t="n">
-        <v>718.0</v>
+        <v>740.0</v>
       </c>
       <c r="O154" t="n">
-        <v>143.0</v>
+        <v>162.0</v>
       </c>
       <c r="P154" t="n">
-        <v>342.0</v>
+        <v>345.0</v>
       </c>
       <c r="Q154" t="n">
         <v>233.0</v>
@@ -11100,7 +11100,7 @@
         <v>1180.0</v>
       </c>
       <c r="J155" t="n">
-        <v>1068.0</v>
+        <v>1069.0</v>
       </c>
       <c r="K155" t="n">
         <v>1.0</v>
@@ -11112,10 +11112,10 @@
         <v>0.0</v>
       </c>
       <c r="N155" t="n">
-        <v>1068.0</v>
+        <v>1069.0</v>
       </c>
       <c r="O155" t="n">
-        <v>543.0</v>
+        <v>544.0</v>
       </c>
       <c r="P155" t="n">
         <v>524.0</v>
@@ -11171,7 +11171,7 @@
         <v>1119.0</v>
       </c>
       <c r="J156" t="n">
-        <v>892.0</v>
+        <v>936.0</v>
       </c>
       <c r="K156" t="n">
         <v>1.0</v>
@@ -11183,13 +11183,13 @@
         <v>0.0</v>
       </c>
       <c r="N156" t="n">
-        <v>892.0</v>
+        <v>936.0</v>
       </c>
       <c r="O156" t="n">
-        <v>402.0</v>
+        <v>445.0</v>
       </c>
       <c r="P156" t="n">
-        <v>489.0</v>
+        <v>490.0</v>
       </c>
       <c r="Q156" t="n">
         <v>1.0</v>
@@ -11242,7 +11242,7 @@
         <v>1501.0</v>
       </c>
       <c r="J157" t="n">
-        <v>1057.0</v>
+        <v>1060.0</v>
       </c>
       <c r="K157" t="n">
         <v>1.0</v>
@@ -11254,10 +11254,10 @@
         <v>4.0</v>
       </c>
       <c r="N157" t="n">
-        <v>1053.0</v>
+        <v>1056.0</v>
       </c>
       <c r="O157" t="n">
-        <v>512.0</v>
+        <v>515.0</v>
       </c>
       <c r="P157" t="n">
         <v>545.0</v>
@@ -11313,7 +11313,7 @@
         <v>1353.0</v>
       </c>
       <c r="J158" t="n">
-        <v>981.0</v>
+        <v>992.0</v>
       </c>
       <c r="K158" t="n">
         <v>1.0</v>
@@ -11325,13 +11325,13 @@
         <v>0.0</v>
       </c>
       <c r="N158" t="n">
-        <v>981.0</v>
+        <v>992.0</v>
       </c>
       <c r="O158" t="n">
-        <v>464.0</v>
+        <v>469.0</v>
       </c>
       <c r="P158" t="n">
-        <v>517.0</v>
+        <v>523.0</v>
       </c>
       <c r="Q158" t="n">
         <v>0.0</v>
@@ -11340,7 +11340,7 @@
         <v>50.0</v>
       </c>
       <c r="S158" t="n">
-        <v>15.0</v>
+        <v>21.0</v>
       </c>
       <c r="T158" t="n">
         <v>0.0</v>
@@ -11352,7 +11352,7 @@
         <v>0.0</v>
       </c>
       <c r="W158" t="n">
-        <v>65.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="159">
@@ -11384,7 +11384,7 @@
         <v>1153.0</v>
       </c>
       <c r="J159" t="n">
-        <v>985.0</v>
+        <v>996.0</v>
       </c>
       <c r="K159" t="n">
         <v>1.0</v>
@@ -11396,13 +11396,13 @@
         <v>1.0</v>
       </c>
       <c r="N159" t="n">
-        <v>984.0</v>
+        <v>995.0</v>
       </c>
       <c r="O159" t="n">
-        <v>578.0</v>
+        <v>584.0</v>
       </c>
       <c r="P159" t="n">
-        <v>407.0</v>
+        <v>412.0</v>
       </c>
       <c r="Q159" t="n">
         <v>0.0</v>
@@ -11597,19 +11597,19 @@
         <v>1184.0</v>
       </c>
       <c r="J162" t="n">
+        <v>979.0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N162" t="n">
         <v>978.0</v>
-      </c>
-      <c r="K162" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L162" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M162" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N162" t="n">
-        <v>977.0</v>
       </c>
       <c r="O162" t="n">
         <v>57.0</v>
@@ -11618,10 +11618,10 @@
         <v>210.0</v>
       </c>
       <c r="Q162" t="n">
-        <v>711.0</v>
+        <v>712.0</v>
       </c>
       <c r="R162" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="S162" t="n">
         <v>0.0</v>
@@ -11636,7 +11636,7 @@
         <v>1.0</v>
       </c>
       <c r="W162" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="163">
@@ -11881,7 +11881,7 @@
         <v>932.0</v>
       </c>
       <c r="J166" t="n">
-        <v>779.0</v>
+        <v>789.0</v>
       </c>
       <c r="K166" t="n">
         <v>1.0</v>
@@ -11893,13 +11893,13 @@
         <v>0.0</v>
       </c>
       <c r="N166" t="n">
-        <v>779.0</v>
+        <v>789.0</v>
       </c>
       <c r="O166" t="n">
-        <v>438.0</v>
+        <v>446.0</v>
       </c>
       <c r="P166" t="n">
-        <v>341.0</v>
+        <v>343.0</v>
       </c>
       <c r="Q166" t="n">
         <v>0.0</v>
@@ -11911,7 +11911,7 @@
         <v>14.0</v>
       </c>
       <c r="T166" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U166" t="n">
         <v>0.0</v>
@@ -11920,7 +11920,7 @@
         <v>0.0</v>
       </c>
       <c r="W166" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="167">
@@ -12378,7 +12378,7 @@
         <v>1266.0</v>
       </c>
       <c r="J173" t="n">
-        <v>1086.0</v>
+        <v>1101.0</v>
       </c>
       <c r="K173" t="n">
         <v>1.0</v>
@@ -12390,13 +12390,13 @@
         <v>0.0</v>
       </c>
       <c r="N173" t="n">
-        <v>1086.0</v>
+        <v>1101.0</v>
       </c>
       <c r="O173" t="n">
-        <v>608.0</v>
+        <v>617.0</v>
       </c>
       <c r="P173" t="n">
-        <v>478.0</v>
+        <v>484.0</v>
       </c>
       <c r="Q173" t="n">
         <v>0.0</v>
@@ -12662,7 +12662,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" t="n">
-        <v>664.0</v>
+        <v>680.0</v>
       </c>
       <c r="K177" t="n">
         <v>1.0</v>
@@ -12674,19 +12674,19 @@
         <v>0.0</v>
       </c>
       <c r="N177" t="n">
-        <v>664.0</v>
+        <v>680.0</v>
       </c>
       <c r="O177" t="n">
-        <v>386.0</v>
+        <v>393.0</v>
       </c>
       <c r="P177" t="n">
-        <v>278.0</v>
+        <v>287.0</v>
       </c>
       <c r="Q177" t="n">
         <v>0.0</v>
       </c>
       <c r="R177" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="S177" t="n">
         <v>24.0</v>
@@ -12701,7 +12701,7 @@
         <v>0.0</v>
       </c>
       <c r="W177" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="178">
@@ -12875,7 +12875,7 @@
         <v>781.0</v>
       </c>
       <c r="J180" t="n">
-        <v>515.0</v>
+        <v>551.0</v>
       </c>
       <c r="K180" t="n">
         <v>1.0</v>
@@ -12887,13 +12887,13 @@
         <v>0.0</v>
       </c>
       <c r="N180" t="n">
-        <v>515.0</v>
+        <v>551.0</v>
       </c>
       <c r="O180" t="n">
-        <v>263.0</v>
+        <v>283.0</v>
       </c>
       <c r="P180" t="n">
-        <v>252.0</v>
+        <v>268.0</v>
       </c>
       <c r="Q180" t="n">
         <v>0.0</v>
@@ -12946,7 +12946,7 @@
         <v>855.0</v>
       </c>
       <c r="J181" t="n">
-        <v>607.0</v>
+        <v>609.0</v>
       </c>
       <c r="K181" t="n">
         <v>1.0</v>
@@ -12958,13 +12958,13 @@
         <v>0.0</v>
       </c>
       <c r="N181" t="n">
-        <v>607.0</v>
+        <v>609.0</v>
       </c>
       <c r="O181" t="n">
         <v>325.0</v>
       </c>
       <c r="P181" t="n">
-        <v>282.0</v>
+        <v>284.0</v>
       </c>
       <c r="Q181" t="n">
         <v>0.0</v>
@@ -13301,7 +13301,7 @@
         <v>1067.0</v>
       </c>
       <c r="J186" t="n">
-        <v>945.0</v>
+        <v>953.0</v>
       </c>
       <c r="K186" t="n">
         <v>1.0</v>
@@ -13313,34 +13313,34 @@
         <v>0.0</v>
       </c>
       <c r="N186" t="n">
-        <v>945.0</v>
+        <v>953.0</v>
       </c>
       <c r="O186" t="n">
-        <v>294.0</v>
+        <v>296.0</v>
       </c>
       <c r="P186" t="n">
         <v>395.0</v>
       </c>
       <c r="Q186" t="n">
-        <v>256.0</v>
+        <v>262.0</v>
       </c>
       <c r="R186" t="n">
         <v>16.0</v>
       </c>
       <c r="S186" t="n">
-        <v>35.0</v>
+        <v>39.0</v>
       </c>
       <c r="T186" t="n">
         <v>0.0</v>
       </c>
       <c r="U186" t="n">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="V186" t="n">
         <v>0.0</v>
       </c>
       <c r="W186" t="n">
-        <v>69.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="187">
@@ -13443,7 +13443,7 @@
         <v>1017.0</v>
       </c>
       <c r="J188" t="n">
-        <v>888.0</v>
+        <v>890.0</v>
       </c>
       <c r="K188" t="n">
         <v>1.0</v>
@@ -13455,13 +13455,13 @@
         <v>0.0</v>
       </c>
       <c r="N188" t="n">
-        <v>888.0</v>
+        <v>890.0</v>
       </c>
       <c r="O188" t="n">
         <v>439.0</v>
       </c>
       <c r="P188" t="n">
-        <v>391.0</v>
+        <v>393.0</v>
       </c>
       <c r="Q188" t="n">
         <v>58.0</v>
@@ -13514,7 +13514,7 @@
         <v>1282.0</v>
       </c>
       <c r="J189" t="n">
-        <v>980.0</v>
+        <v>1046.0</v>
       </c>
       <c r="K189" t="n">
         <v>1.0</v>
@@ -13526,13 +13526,13 @@
         <v>0.0</v>
       </c>
       <c r="N189" t="n">
-        <v>980.0</v>
+        <v>1046.0</v>
       </c>
       <c r="O189" t="n">
-        <v>381.0</v>
+        <v>436.0</v>
       </c>
       <c r="P189" t="n">
-        <v>325.0</v>
+        <v>336.0</v>
       </c>
       <c r="Q189" t="n">
         <v>274.0</v>
@@ -13544,7 +13544,7 @@
         <v>5.0</v>
       </c>
       <c r="T189" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="U189" t="n">
         <v>0.0</v>
@@ -13553,7 +13553,7 @@
         <v>0.0</v>
       </c>
       <c r="W189" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="190">
@@ -13656,7 +13656,7 @@
         <v>1363.0</v>
       </c>
       <c r="J191" t="n">
-        <v>1150.0</v>
+        <v>1184.0</v>
       </c>
       <c r="K191" t="n">
         <v>1.0</v>
@@ -13668,16 +13668,16 @@
         <v>0.0</v>
       </c>
       <c r="N191" t="n">
-        <v>1150.0</v>
+        <v>1184.0</v>
       </c>
       <c r="O191" t="n">
-        <v>662.0</v>
+        <v>685.0</v>
       </c>
       <c r="P191" t="n">
-        <v>454.0</v>
+        <v>461.0</v>
       </c>
       <c r="Q191" t="n">
-        <v>34.0</v>
+        <v>38.0</v>
       </c>
       <c r="R191" t="n">
         <v>47.0</v>
@@ -13686,7 +13686,7 @@
         <v>14.0</v>
       </c>
       <c r="T191" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U191" t="n">
         <v>0.0</v>
@@ -13695,7 +13695,7 @@
         <v>0.0</v>
       </c>
       <c r="W191" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="192">
@@ -13727,7 +13727,7 @@
         <v>508.0</v>
       </c>
       <c r="J192" t="n">
-        <v>461.0</v>
+        <v>463.0</v>
       </c>
       <c r="K192" t="n">
         <v>1.0</v>
@@ -13739,10 +13739,10 @@
         <v>0.0</v>
       </c>
       <c r="N192" t="n">
-        <v>461.0</v>
+        <v>463.0</v>
       </c>
       <c r="O192" t="n">
-        <v>287.0</v>
+        <v>289.0</v>
       </c>
       <c r="P192" t="n">
         <v>169.0</v>
@@ -13798,7 +13798,7 @@
         <v>1326.0</v>
       </c>
       <c r="J193" t="n">
-        <v>1172.0</v>
+        <v>1180.0</v>
       </c>
       <c r="K193" t="n">
         <v>1.0</v>
@@ -13810,13 +13810,13 @@
         <v>0.0</v>
       </c>
       <c r="N193" t="n">
-        <v>1172.0</v>
+        <v>1180.0</v>
       </c>
       <c r="O193" t="n">
-        <v>438.0</v>
+        <v>442.0</v>
       </c>
       <c r="P193" t="n">
-        <v>516.0</v>
+        <v>520.0</v>
       </c>
       <c r="Q193" t="n">
         <v>218.0</v>
@@ -13940,7 +13940,7 @@
         <v>556.0</v>
       </c>
       <c r="J195" t="n">
-        <v>516.0</v>
+        <v>521.0</v>
       </c>
       <c r="K195" t="n">
         <v>1.0</v>
@@ -13952,22 +13952,22 @@
         <v>0.0</v>
       </c>
       <c r="N195" t="n">
-        <v>516.0</v>
+        <v>521.0</v>
       </c>
       <c r="O195" t="n">
-        <v>186.0</v>
+        <v>190.0</v>
       </c>
       <c r="P195" t="n">
-        <v>203.0</v>
+        <v>204.0</v>
       </c>
       <c r="Q195" t="n">
         <v>127.0</v>
       </c>
       <c r="R195" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="S195" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T195" t="n">
         <v>0.0</v>
@@ -13979,7 +13979,7 @@
         <v>0.0</v>
       </c>
       <c r="W195" t="n">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="196">
@@ -14153,7 +14153,7 @@
         <v>1477.0</v>
       </c>
       <c r="J198" t="n">
-        <v>1286.0</v>
+        <v>1290.0</v>
       </c>
       <c r="K198" t="n">
         <v>1.0</v>
@@ -14165,13 +14165,13 @@
         <v>0.0</v>
       </c>
       <c r="N198" t="n">
-        <v>1286.0</v>
+        <v>1290.0</v>
       </c>
       <c r="O198" t="n">
-        <v>380.0</v>
+        <v>383.0</v>
       </c>
       <c r="P198" t="n">
-        <v>630.0</v>
+        <v>631.0</v>
       </c>
       <c r="Q198" t="n">
         <v>276.0</v>
@@ -14295,7 +14295,7 @@
         <v>704.0</v>
       </c>
       <c r="J200" t="n">
-        <v>599.0</v>
+        <v>604.0</v>
       </c>
       <c r="K200" t="n">
         <v>1.0</v>
@@ -14307,13 +14307,13 @@
         <v>0.0</v>
       </c>
       <c r="N200" t="n">
-        <v>599.0</v>
+        <v>604.0</v>
       </c>
       <c r="O200" t="n">
-        <v>351.0</v>
+        <v>353.0</v>
       </c>
       <c r="P200" t="n">
-        <v>245.0</v>
+        <v>248.0</v>
       </c>
       <c r="Q200" t="n">
         <v>3.0</v>
@@ -14366,7 +14366,7 @@
         <v>1283.0</v>
       </c>
       <c r="J201" t="n">
-        <v>1167.0</v>
+        <v>1174.0</v>
       </c>
       <c r="K201" t="n">
         <v>1.0</v>
@@ -14378,13 +14378,13 @@
         <v>0.0</v>
       </c>
       <c r="N201" t="n">
-        <v>1167.0</v>
+        <v>1174.0</v>
       </c>
       <c r="O201" t="n">
-        <v>621.0</v>
+        <v>624.0</v>
       </c>
       <c r="P201" t="n">
-        <v>534.0</v>
+        <v>538.0</v>
       </c>
       <c r="Q201" t="n">
         <v>12.0</v>
@@ -14437,7 +14437,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" t="n">
-        <v>959.0</v>
+        <v>997.0</v>
       </c>
       <c r="K202" t="n">
         <v>1.0</v>
@@ -14449,13 +14449,13 @@
         <v>0.0</v>
       </c>
       <c r="N202" t="n">
-        <v>959.0</v>
+        <v>997.0</v>
       </c>
       <c r="O202" t="n">
-        <v>582.0</v>
+        <v>606.0</v>
       </c>
       <c r="P202" t="n">
-        <v>377.0</v>
+        <v>391.0</v>
       </c>
       <c r="Q202" t="n">
         <v>0.0</v>
@@ -14650,7 +14650,7 @@
         <v>897.0</v>
       </c>
       <c r="J205" t="n">
-        <v>702.0</v>
+        <v>704.0</v>
       </c>
       <c r="K205" t="n">
         <v>1.0</v>
@@ -14662,10 +14662,10 @@
         <v>0.0</v>
       </c>
       <c r="N205" t="n">
-        <v>702.0</v>
+        <v>704.0</v>
       </c>
       <c r="O205" t="n">
-        <v>368.0</v>
+        <v>370.0</v>
       </c>
       <c r="P205" t="n">
         <v>287.0</v>
@@ -14677,19 +14677,19 @@
         <v>21.0</v>
       </c>
       <c r="S205" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="T205" t="n">
         <v>0.0</v>
       </c>
       <c r="U205" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V205" t="n">
         <v>0.0</v>
       </c>
       <c r="W205" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="206">
@@ -14792,7 +14792,7 @@
         <v>943.0</v>
       </c>
       <c r="J207" t="n">
-        <v>710.0</v>
+        <v>726.0</v>
       </c>
       <c r="K207" t="n">
         <v>1.0</v>
@@ -14804,22 +14804,22 @@
         <v>0.0</v>
       </c>
       <c r="N207" t="n">
-        <v>710.0</v>
+        <v>726.0</v>
       </c>
       <c r="O207" t="n">
-        <v>394.0</v>
+        <v>403.0</v>
       </c>
       <c r="P207" t="n">
-        <v>304.0</v>
+        <v>311.0</v>
       </c>
       <c r="Q207" t="n">
         <v>12.0</v>
       </c>
       <c r="R207" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="S207" t="n">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
       <c r="T207" t="n">
         <v>0.0</v>
@@ -14831,7 +14831,7 @@
         <v>0.0</v>
       </c>
       <c r="W207" t="n">
-        <v>53.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="208">
@@ -15147,7 +15147,7 @@
         <v>1055.0</v>
       </c>
       <c r="J212" t="n">
-        <v>892.0</v>
+        <v>905.0</v>
       </c>
       <c r="K212" t="n">
         <v>1.0</v>
@@ -15159,13 +15159,13 @@
         <v>1.0</v>
       </c>
       <c r="N212" t="n">
-        <v>891.0</v>
+        <v>904.0</v>
       </c>
       <c r="O212" t="n">
-        <v>277.0</v>
+        <v>283.0</v>
       </c>
       <c r="P212" t="n">
-        <v>395.0</v>
+        <v>402.0</v>
       </c>
       <c r="Q212" t="n">
         <v>220.0</v>
@@ -15174,19 +15174,19 @@
         <v>100.0</v>
       </c>
       <c r="S212" t="n">
-        <v>21.0</v>
+        <v>24.0</v>
       </c>
       <c r="T212" t="n">
         <v>0.0</v>
       </c>
       <c r="U212" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="V212" t="n">
         <v>0.0</v>
       </c>
       <c r="W212" t="n">
-        <v>121.0</v>
+        <v>129.0</v>
       </c>
     </row>
     <row r="213">
@@ -15289,7 +15289,7 @@
         <v>1038.0</v>
       </c>
       <c r="J214" t="n">
-        <v>802.0</v>
+        <v>808.0</v>
       </c>
       <c r="K214" t="n">
         <v>1.0</v>
@@ -15301,13 +15301,13 @@
         <v>0.0</v>
       </c>
       <c r="N214" t="n">
-        <v>802.0</v>
+        <v>808.0</v>
       </c>
       <c r="O214" t="n">
-        <v>423.0</v>
+        <v>426.0</v>
       </c>
       <c r="P214" t="n">
-        <v>379.0</v>
+        <v>382.0</v>
       </c>
       <c r="Q214" t="n">
         <v>0.0</v>
@@ -15360,7 +15360,7 @@
         <v>1067.0</v>
       </c>
       <c r="J215" t="n">
-        <v>965.0</v>
+        <v>983.0</v>
       </c>
       <c r="K215" t="n">
         <v>1.0</v>
@@ -15372,22 +15372,22 @@
         <v>0.0</v>
       </c>
       <c r="N215" t="n">
-        <v>965.0</v>
+        <v>983.0</v>
       </c>
       <c r="O215" t="n">
-        <v>490.0</v>
+        <v>496.0</v>
       </c>
       <c r="P215" t="n">
-        <v>465.0</v>
+        <v>469.0</v>
       </c>
       <c r="Q215" t="n">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="R215" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="S215" t="n">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="T215" t="n">
         <v>7.0</v>
@@ -15399,7 +15399,7 @@
         <v>0.0</v>
       </c>
       <c r="W215" t="n">
-        <v>62.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="216">
@@ -15502,7 +15502,7 @@
         <v>1136.0</v>
       </c>
       <c r="J217" t="n">
-        <v>787.0</v>
+        <v>791.0</v>
       </c>
       <c r="K217" t="n">
         <v>1.0</v>
@@ -15514,13 +15514,13 @@
         <v>0.0</v>
       </c>
       <c r="N217" t="n">
-        <v>787.0</v>
+        <v>791.0</v>
       </c>
       <c r="O217" t="n">
-        <v>399.0</v>
+        <v>401.0</v>
       </c>
       <c r="P217" t="n">
-        <v>388.0</v>
+        <v>390.0</v>
       </c>
       <c r="Q217" t="n">
         <v>0.0</v>
@@ -15644,7 +15644,7 @@
         <v>1433.0</v>
       </c>
       <c r="J219" t="n">
-        <v>1053.0</v>
+        <v>1065.0</v>
       </c>
       <c r="K219" t="n">
         <v>1.0</v>
@@ -15656,13 +15656,13 @@
         <v>0.0</v>
       </c>
       <c r="N219" t="n">
-        <v>1053.0</v>
+        <v>1065.0</v>
       </c>
       <c r="O219" t="n">
-        <v>221.0</v>
+        <v>227.0</v>
       </c>
       <c r="P219" t="n">
-        <v>451.0</v>
+        <v>457.0</v>
       </c>
       <c r="Q219" t="n">
         <v>381.0</v>
@@ -15715,7 +15715,7 @@
         <v>867.0</v>
       </c>
       <c r="J220" t="n">
-        <v>707.0</v>
+        <v>743.0</v>
       </c>
       <c r="K220" t="n">
         <v>1.0</v>
@@ -15727,13 +15727,13 @@
         <v>0.0</v>
       </c>
       <c r="N220" t="n">
-        <v>707.0</v>
+        <v>743.0</v>
       </c>
       <c r="O220" t="n">
-        <v>157.0</v>
+        <v>174.0</v>
       </c>
       <c r="P220" t="n">
-        <v>317.0</v>
+        <v>336.0</v>
       </c>
       <c r="Q220" t="n">
         <v>233.0</v>
@@ -15857,7 +15857,7 @@
         <v>1043.0</v>
       </c>
       <c r="J222" t="n">
-        <v>897.0</v>
+        <v>916.0</v>
       </c>
       <c r="K222" t="n">
         <v>1.0</v>
@@ -15869,13 +15869,13 @@
         <v>0.0</v>
       </c>
       <c r="N222" t="n">
-        <v>897.0</v>
+        <v>916.0</v>
       </c>
       <c r="O222" t="n">
-        <v>261.0</v>
+        <v>266.0</v>
       </c>
       <c r="P222" t="n">
-        <v>385.0</v>
+        <v>399.0</v>
       </c>
       <c r="Q222" t="n">
         <v>251.0</v>
@@ -16212,7 +16212,7 @@
         <v>428.0</v>
       </c>
       <c r="J227" t="n">
-        <v>368.0</v>
+        <v>372.0</v>
       </c>
       <c r="K227" t="n">
         <v>1.0</v>
@@ -16224,13 +16224,13 @@
         <v>0.0</v>
       </c>
       <c r="N227" t="n">
-        <v>368.0</v>
+        <v>372.0</v>
       </c>
       <c r="O227" t="n">
         <v>236.0</v>
       </c>
       <c r="P227" t="n">
-        <v>132.0</v>
+        <v>136.0</v>
       </c>
       <c r="Q227" t="n">
         <v>0.0</v>
@@ -16242,7 +16242,7 @@
         <v>6.0</v>
       </c>
       <c r="T227" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U227" t="n">
         <v>0.0</v>
@@ -16251,7 +16251,7 @@
         <v>0.0</v>
       </c>
       <c r="W227" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="228">
@@ -16283,7 +16283,7 @@
         <v>1402.0</v>
       </c>
       <c r="J228" t="n">
-        <v>993.0</v>
+        <v>1012.0</v>
       </c>
       <c r="K228" t="n">
         <v>1.0</v>
@@ -16295,13 +16295,13 @@
         <v>0.0</v>
       </c>
       <c r="N228" t="n">
-        <v>993.0</v>
+        <v>1012.0</v>
       </c>
       <c r="O228" t="n">
-        <v>264.0</v>
+        <v>274.0</v>
       </c>
       <c r="P228" t="n">
-        <v>396.0</v>
+        <v>405.0</v>
       </c>
       <c r="Q228" t="n">
         <v>333.0</v>
@@ -16567,7 +16567,7 @@
         <v>1369.0</v>
       </c>
       <c r="J232" t="n">
-        <v>934.0</v>
+        <v>982.0</v>
       </c>
       <c r="K232" t="n">
         <v>1.0</v>
@@ -16579,16 +16579,16 @@
         <v>0.0</v>
       </c>
       <c r="N232" t="n">
-        <v>934.0</v>
+        <v>982.0</v>
       </c>
       <c r="O232" t="n">
-        <v>111.0</v>
+        <v>130.0</v>
       </c>
       <c r="P232" t="n">
-        <v>185.0</v>
+        <v>204.0</v>
       </c>
       <c r="Q232" t="n">
-        <v>638.0</v>
+        <v>648.0</v>
       </c>
       <c r="R232" t="n">
         <v>31.0</v>
